--- a/storage/seeders/questions.xlsx
+++ b/storage/seeders/questions.xlsx
@@ -2,18 +2,21 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7635"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$76</definedName>
+  </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -24,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="355">
   <si>
     <t>પ્રશ્ન</t>
   </si>
@@ -59,9 +62,6 @@
     <t>પંઢરપુર ના પાંડુરંગ ક્યાં નદી ના કિનારે ઉભા છે?</t>
   </si>
   <si>
-    <t>ભીમા</t>
-  </si>
-  <si>
     <t>નર્મદા</t>
   </si>
   <si>
@@ -200,9 +200,6 @@
     <t>ભાનુદાસ</t>
   </si>
   <si>
-    <t>રોહીદાસ</t>
-  </si>
-  <si>
     <t>રામદાસ</t>
   </si>
   <si>
@@ -299,9 +296,6 @@
     <t>પંચવટી</t>
   </si>
   <si>
-    <t>ભગવાને પોતાની વિભૂતિઓ નું વર્ણન કરતા કહ્યું છે કે દેવો ના ............... હું છુ</t>
-  </si>
-  <si>
     <t>ઇન્દ્ર</t>
   </si>
   <si>
@@ -338,26 +332,810 @@
     <t>type</t>
   </si>
   <si>
-    <t>મધ્યમ</t>
-  </si>
-  <si>
-    <t>ઉચ્ચ</t>
-  </si>
-  <si>
     <t>reference</t>
   </si>
   <si>
-    <t>સરળ</t>
-  </si>
-  <si>
     <t>RANK</t>
+  </si>
+  <si>
+    <t>કરન્ધમ</t>
+  </si>
+  <si>
+    <t>અવિક્ષિત</t>
+  </si>
+  <si>
+    <t>ગુણાઢય</t>
+  </si>
+  <si>
+    <t>વાજ્શ્રવસ</t>
+  </si>
+  <si>
+    <t>શ્રાદ્ધ ભાગ ૨</t>
+  </si>
+  <si>
+    <t>સર્વદક્ષિણા દાન કરનારન કોણ હતું?</t>
+  </si>
+  <si>
+    <t>પૃથ્વીમાતા ના રત્નો પાછા લાવનાર કોણ હતું?</t>
+  </si>
+  <si>
+    <t>અત્રિ</t>
+  </si>
+  <si>
+    <t>મરીચી</t>
+  </si>
+  <si>
+    <t>અગસ્તિ</t>
+  </si>
+  <si>
+    <t>કશ્યપ</t>
+  </si>
+  <si>
+    <t>કૃતજ્ઞતા પૂર્વક પિતૃઓનું સ્મરણ કરવાના દિવસો?</t>
+  </si>
+  <si>
+    <t>ઋષીપંચમી</t>
+  </si>
+  <si>
+    <t>ગુરુપૂર્ણિમા</t>
+  </si>
+  <si>
+    <t>શ્રાદ્ધ</t>
+  </si>
+  <si>
+    <t>માતૃદિન</t>
+  </si>
+  <si>
+    <t>જીવન ની ઘોર સુષુપ્તિ માંથી જાગવાનો સંદેશ આપતી એકાદશી?</t>
+  </si>
+  <si>
+    <t>પ્રબોધિની એકાદશી</t>
+  </si>
+  <si>
+    <t>દેવશયની એકાદશી</t>
+  </si>
+  <si>
+    <t>કારતક સુદ એકાદશી</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>A અને C બન્ને</t>
+    </r>
+  </si>
+  <si>
+    <t>સ્ત્રી ને સૌભાગ્ય આપનાર તેમજ પુત્રવતી બનાવનાર અમાસ એટલે</t>
+  </si>
+  <si>
+    <t>શ્રાવણ વદ અમાસ</t>
+  </si>
+  <si>
+    <t>ભાદરવા વદ અમાસ</t>
+  </si>
+  <si>
+    <t>આસો વદ અમાસ</t>
+  </si>
+  <si>
+    <t>અષાઢ વદ અમાસ</t>
+  </si>
+  <si>
+    <t>દસ પાપો નું હરણ કરનારઉત્સવ એટલે?</t>
+  </si>
+  <si>
+    <t>દશેરા</t>
+  </si>
+  <si>
+    <t>ગંગા દશહરા</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A અને B બન્ને</t>
+  </si>
+  <si>
+    <t>શ્રાવણી પૂર્ણિમા</t>
+  </si>
+  <si>
+    <t>શક્તિ ઉપાસના ના દિવસો ?</t>
+  </si>
+  <si>
+    <t>ગીતા જયંતી</t>
+  </si>
+  <si>
+    <t>નવરાત્રી</t>
+  </si>
+  <si>
+    <t>શરદ પૂર્ણિમા</t>
+  </si>
+  <si>
+    <t>ચૈત્રી નવરાત્રી</t>
+  </si>
+  <si>
+    <t>નાગપંચમી</t>
+  </si>
+  <si>
+    <t>વિજયાદશમી</t>
+  </si>
+  <si>
+    <t>ગુડીપડવો</t>
+  </si>
+  <si>
+    <t>શીતળાસાતમ</t>
+  </si>
+  <si>
+    <t>ભાદરવા સુદ પાંચમ નો દિવસ</t>
+  </si>
+  <si>
+    <t>વસંત પંચમી</t>
+  </si>
+  <si>
+    <t>શાક્ય વંશ માં જન્મ લેનાર અવતાર</t>
+  </si>
+  <si>
+    <t>વામનાવતાર</t>
+  </si>
+  <si>
+    <t>પરશુરામાવાતર</t>
+  </si>
+  <si>
+    <t>મત્સ્યાવતાર</t>
+  </si>
+  <si>
+    <t>બુદ્ધાવતાર</t>
+  </si>
+  <si>
+    <t>અદિતિ ના પેટે જન્મ લેનાર અવતાર</t>
+  </si>
+  <si>
+    <t>કુર્માવતાર</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>પરશુરામે સમસ્ત પૃથ્વી જેને દાનમાં આપી તે ઋષી એટલે</t>
+  </si>
+  <si>
+    <t>વશિષ્ઠ</t>
+  </si>
+  <si>
+    <t>વિશ્વામિત્ર</t>
+  </si>
+  <si>
+    <t>શંકરાચાર્ય</t>
+  </si>
+  <si>
+    <t>મહાવીર</t>
+  </si>
+  <si>
+    <t>હનુમાન</t>
+  </si>
+  <si>
+    <t>સેવક અને સૈનિક નો સંયોગ જેનામાં છે તેવા ભક્ત</t>
+  </si>
+  <si>
+    <t>જ્ઞાન અને ભાવ નો સુભગ સમન્વય ક્યાં આચાર્ય માં જોવા મળે છે?</t>
+  </si>
+  <si>
+    <t>વલ્લભાચાર્ય</t>
+  </si>
+  <si>
+    <t>રામાનુજાચાર્ય</t>
+  </si>
+  <si>
+    <t>માધવાચાર્ય</t>
+  </si>
+  <si>
+    <t>નંદી</t>
+  </si>
+  <si>
+    <t>મોર</t>
+  </si>
+  <si>
+    <t>કાચબો</t>
+  </si>
+  <si>
+    <t>ગરુડ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">મહત્વાકાંક્ષા લઇ જીવન જીવતા, સ્વર્ગમાં પણ સ્થાન અપાવતા , થયા જગતમા ભગવાનના ગુરુ નામે પ્રસીદ્ધ, તે એટલે.... </t>
+  </si>
+  <si>
+    <t>ઋષીસ્મરણ</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>યોગેશ્વર કૃષિ</t>
+  </si>
+  <si>
+    <t>વૃક્ષમંદિર</t>
+  </si>
+  <si>
+    <t>મત્સ્યગંધા</t>
+  </si>
+  <si>
+    <t>શ્રીદર્શનમ</t>
+  </si>
+  <si>
+    <t>Hard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">હર્ષ-ઉલ્લાસ ને બાથ ભરવા , રંગબેરંગી આકાશે ઉડવા , નમસ્કાર શ્રુતિ-સ્મૃતિ વૈચારિક પ્રવાહ, ઘર ઘર પ્રયાસ કરે ગગન ચુંબવા. </t>
+  </si>
+  <si>
+    <t>સુધાવર્ષ</t>
+  </si>
+  <si>
+    <t>કૃતજ્ઞતા સમારોહ</t>
+  </si>
+  <si>
+    <t>અશીતિ વંદના</t>
+  </si>
+  <si>
+    <t>તીર્થરાજ મિલન</t>
+  </si>
+  <si>
+    <t>મળ્યા છે વેદ ના વિચાર ગર્ભથી, इहैव स्वर्गः થી માનવી જીવન નું સાફલ્ય કહી આપે દસ સિધ્ધાંત, તે ઋષી એટલે....</t>
+  </si>
+  <si>
+    <t>મનુ</t>
+  </si>
+  <si>
+    <t>વેદવ્યાસ</t>
+  </si>
+  <si>
+    <t>યાજ્ઞવલ્ક્ય</t>
+  </si>
+  <si>
+    <t>પરાશર</t>
+  </si>
+  <si>
+    <t>તૈયાર કરીએ કાર્ડ, મળીયે હાર્ટ-ટુ-હાર્ટ, પાલક ને લેવા કાળજી, કહીએ તમે પણ પધારશોજી</t>
+  </si>
+  <si>
+    <t>ક્ષેત્ર મિલન</t>
+  </si>
+  <si>
+    <t>વેલકમ મિલન</t>
+  </si>
+  <si>
+    <t>દીર્ઘ મિલન</t>
+  </si>
+  <si>
+    <t>એક પણ નહિ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">लिया वहा रख , सोचा तब कर , स्वच्छ बना दे दुनिया , प्रभु घरमे है बसा </t>
+  </si>
+  <si>
+    <t xml:space="preserve">યુવાદિન </t>
+  </si>
+  <si>
+    <t xml:space="preserve">મનુષ્ય ગૌરવ દિન </t>
+  </si>
+  <si>
+    <t xml:space="preserve">વર્ષામિલન </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>વર્ષામિલન</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t>मन को प्रफुल्लित रख , आत्मविश्वास को कर उन्नत , गौरव होगा तेरा जग मे, फिरभी सम्मान करना सबका</t>
+  </si>
+  <si>
+    <t xml:space="preserve">હલ્દી કંકુ મિલન </t>
+  </si>
+  <si>
+    <t xml:space="preserve">વૃક્ષ મંદિર દિન </t>
+  </si>
+  <si>
+    <t>ક્યાં અવતાર માનવેતર યોની કરતા જુદી યોની માં થયો છે?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">રામ </t>
+  </si>
+  <si>
+    <t>બુદ્ધ</t>
+  </si>
+  <si>
+    <t>કલ્કી</t>
+  </si>
+  <si>
+    <t>વરાહ</t>
+  </si>
+  <si>
+    <t>દશાવતાર</t>
+  </si>
+  <si>
+    <t>મેઘદૂત</t>
+  </si>
+  <si>
+    <t>શાન્કુતાલમ</t>
+  </si>
+  <si>
+    <t>કુમારસંભવમ</t>
+  </si>
+  <si>
+    <t>શિશુપાલવધ</t>
+  </si>
+  <si>
+    <t>પાંડુરંગ ભગવાન નું સ્તવન શંકરાચાર્ય એ ક્યાં નદી ના કિનારે બેસીને ગાયેલું છે?</t>
+  </si>
+  <si>
+    <t>ગોમતી</t>
+  </si>
+  <si>
+    <t>કૃષ્ણા</t>
+  </si>
+  <si>
+    <t>ભીમારથી</t>
+  </si>
+  <si>
+    <t>પાંડુરંગાષ્ટકમ</t>
+  </si>
+  <si>
+    <t>રામાયણ ના અંત માં કાલપુરુષ કયું રૂપ લઇ ને આવે છે ?</t>
+  </si>
+  <si>
+    <t>બ્રાહ્મણ</t>
+  </si>
+  <si>
+    <t>ક્ષત્રિય</t>
+  </si>
+  <si>
+    <t>વૈશ્ય</t>
+  </si>
+  <si>
+    <t>ક્ષુદ્ર</t>
+  </si>
+  <si>
+    <t>વાલ્મીકિ રામાયણ</t>
+  </si>
+  <si>
+    <t>રુતુદ્વાજ ના પત્ની નું નામ શું હતું?</t>
+  </si>
+  <si>
+    <t>રત્નાવલી</t>
+  </si>
+  <si>
+    <t>મદાલસા</t>
+  </si>
+  <si>
+    <t>ચંદ્રા</t>
+  </si>
+  <si>
+    <t>શાંતા</t>
+  </si>
+  <si>
+    <t>શ્રાધ ભાગ -૧</t>
+  </si>
+  <si>
+    <t>હિરણ્યકશિપું એ પ્રહલાદ ને ક્યાં શિક્ષક પાસે અભ્યાસ મેળવવા મોકલ્યો હતો?</t>
+  </si>
+  <si>
+    <t>શિશુપાલ</t>
+  </si>
+  <si>
+    <t>શુંડામર્ક</t>
+  </si>
+  <si>
+    <t>રામકાળ માં કેટલા પ્રકારના વેપાર ધંધા હતા?</t>
+  </si>
+  <si>
+    <t>સોનું</t>
+  </si>
+  <si>
+    <t>ચાંદી</t>
+  </si>
+  <si>
+    <t>તાંબુ</t>
+  </si>
+  <si>
+    <t>પિતળ</t>
+  </si>
+  <si>
+    <t>આમાંથી કોની નવમી પેઢીમાં ભગવાન શ્રીકૃષ્ણ એ જન્મ લીધો હતો?</t>
+  </si>
+  <si>
+    <t>નભગ</t>
+  </si>
+  <si>
+    <t>શ્રાધ ભાગ -૨</t>
+  </si>
+  <si>
+    <t>નચિકેતા ના પિતાનું નામ શું છે?</t>
+  </si>
+  <si>
+    <t>મરુત</t>
+  </si>
+  <si>
+    <t>ઇન્દ્રસેન</t>
+  </si>
+  <si>
+    <t>રામકાલીન સમાજના  લોકો ની જીવનશૈલીનું વર્ણન ક્યાં કાંડ માં છે?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">બાલકાંડ </t>
+  </si>
+  <si>
+    <t>સુંદરકાંડ</t>
+  </si>
+  <si>
+    <t>કિષ્કિંધાકાંડ</t>
+  </si>
+  <si>
+    <t>અરણ્યકાંડ</t>
+  </si>
+  <si>
+    <t>ગીતગોવિંદ કોણે ગાયું છે?</t>
+  </si>
+  <si>
+    <t>ભક્તકવિ જયદેવ</t>
+  </si>
+  <si>
+    <t>વિરોચન ના પુત્ર નું નામ શું હતું?</t>
+  </si>
+  <si>
+    <t>બલિ</t>
+  </si>
+  <si>
+    <t>પ્રહલાદ</t>
+  </si>
+  <si>
+    <t>હિરણ્યકશિપું</t>
+  </si>
+  <si>
+    <t>હિરણ્યાક્ષ</t>
+  </si>
+  <si>
+    <t>મહાન શિવભક્ત શાપિત પુષ્પદંત નો બીજો જન્મ કયો ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">હર્ષ </t>
+  </si>
+  <si>
+    <t>વરરુચી</t>
+  </si>
+  <si>
+    <t>ઇન્દ્રદત્ત</t>
+  </si>
+  <si>
+    <t>વ્યાડી</t>
+  </si>
+  <si>
+    <t>હંસ અને ડીંભક કોના શેનાપતી હતા?</t>
+  </si>
+  <si>
+    <t>કંસ</t>
+  </si>
+  <si>
+    <t>જરાસંઘ</t>
+  </si>
+  <si>
+    <t>રાવણ</t>
+  </si>
+  <si>
+    <t>બલરામ</t>
+  </si>
+  <si>
+    <t>દૈત્યો ના ગુરૂ કોણ હતા?</t>
+  </si>
+  <si>
+    <t>દ્રોણાચાર્ય</t>
+  </si>
+  <si>
+    <t>કૃપાચાર્ય</t>
+  </si>
+  <si>
+    <t>ભાર્ગવરામ એટલે કોણ?</t>
+  </si>
+  <si>
+    <t>શ્રીરામ</t>
+  </si>
+  <si>
+    <t>શ્રીકૃષ્ણ</t>
+  </si>
+  <si>
+    <t>પરશુરામ</t>
+  </si>
+  <si>
+    <t>ક્યા વ્યક્તિ ના વિરોધ કરવાથી શ્રીકૃષ્ણ ભગવાન રણ છોડીને ભાગ્યા હતા?</t>
+  </si>
+  <si>
+    <t>અક્રુરજી</t>
+  </si>
+  <si>
+    <t>વસુદેવ</t>
+  </si>
+  <si>
+    <t>ઉગ્રસેન</t>
+  </si>
+  <si>
+    <t>વિક્દ્રુ</t>
+  </si>
+  <si>
+    <t>કૌરવો તરફથી વિષ્ટિ કરવા કોણ આવ્યું હતું?</t>
+  </si>
+  <si>
+    <t>સંજય</t>
+  </si>
+  <si>
+    <t>શકુની</t>
+  </si>
+  <si>
+    <t>દુર્યોધન</t>
+  </si>
+  <si>
+    <t>વિદુરજી</t>
+  </si>
+  <si>
+    <t>સંત તુલસીદાસ ના પત્ની નું નામ શું હતું?</t>
+  </si>
+  <si>
+    <t>સાન્તા</t>
+  </si>
+  <si>
+    <t xml:space="preserve">શક્તિ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">તેજ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">લક્ષ્મી </t>
+  </si>
+  <si>
+    <t xml:space="preserve">જ્ઞાન </t>
+  </si>
+  <si>
+    <t xml:space="preserve">સંસ્કૃતિ પૂજન </t>
+  </si>
+  <si>
+    <t>ભગવાન વિષ્ણુના હાથમાં રહેલ શંખ ક્યાં વર્ગનો દ્યોતક છે ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ક્ષત્રિય </t>
+  </si>
+  <si>
+    <t xml:space="preserve">બ્રામ્હણ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">વૈશ્ય </t>
+  </si>
+  <si>
+    <t xml:space="preserve">શુદ્ર </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ૐ કેટલા અક્ષરનો બનેલો શબ્દ છે ? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">બે </t>
+  </si>
+  <si>
+    <t xml:space="preserve">અઢી </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ત્રણ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">સાડા ત્રણ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARRIAGE શબ્દ લગ્નજીવનમાં આવશ્યક ગુણોનું સૂચન કરે છે તે ગુણ નીચેનામાંથી કયો નથી ? (રેફરન્સ સંસ્કૃતિ પૂજન) </t>
+  </si>
+  <si>
+    <t>E-EFFICIENCY-કાર્યક્ષમતા</t>
+  </si>
+  <si>
+    <t>R-RESPONSE-આવકાર (સ્વાગત)</t>
+  </si>
+  <si>
+    <t>A-AMBITION-મહત્વકાંક્ષા</t>
+  </si>
+  <si>
+    <t>E-ETERNITY-શાશ્વતતા</t>
+  </si>
+  <si>
+    <t>ભૌતિક જીવન સુખી કરવા માટે નીચેના માંથી કઈ મુખ્ય વાત નથી ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">મન-બુદ્ધિની શુધ્ધતા </t>
+  </si>
+  <si>
+    <t xml:space="preserve">નિશ્ચિંત જીવન </t>
+  </si>
+  <si>
+    <t xml:space="preserve">અનુકુળ પત્ની </t>
+  </si>
+  <si>
+    <t xml:space="preserve">આનંદદાયની વિદ્યા </t>
+  </si>
+  <si>
+    <t>પંચાયતન પુજાના પાંચ દેવોમાં હરી એટલે .....</t>
+  </si>
+  <si>
+    <t>રામકાળમાં કઈ ધાતુનું ચલણી નાણું હતું?</t>
+  </si>
+  <si>
+    <t>નીચેના માંથી  કયું કાવ્ય કાલિદાસ નું નથી?</t>
+  </si>
+  <si>
+    <t>વિશ્વના પ્રશ્નોને દેવા જવાબ, લોક હૃદય થી લાવી બહાર, વૃક્ષ માં જુવે વાસુદેવ, જુઓ પથરાવે મીઠાસ કાહી, પાવડા ત્રિકમ થી રચે કમાલ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">કરે લોક નિર્ધાર, પ્રસન્ન કરવા ભગવાન , બનાવીએ વર્ષ યાદગાર , અક્ષયતૃતીયા ના દિવસે કંકુ ચોખા લઇ સાથ સાથ </t>
+  </si>
+  <si>
+    <t>નીચેનામાંથી કયો જીવ ઇન્દ્રિય નિગ્રહ અને સંયમ નું પ્રતિક છે</t>
+  </si>
+  <si>
+    <t>સાધન પૂજન નો મહિમા સમજાવતો ઉત્સવ એટલે...</t>
+  </si>
+  <si>
+    <t>ભગવાને પોતાની વિભૂતિઓ નું વર્ણન કરતા કહ્યું છે કે દેવો માં ............... હું છુ</t>
+  </si>
+  <si>
+    <t>ભક્ત કવિજયદેવ</t>
+  </si>
+  <si>
+    <t>સુર્યપાણી</t>
+  </si>
+  <si>
+    <t>ચક્રપાણી</t>
+  </si>
+  <si>
+    <t>પર્વ</t>
+  </si>
+  <si>
+    <t>કવિ સુરદાસ</t>
+  </si>
+  <si>
+    <t>કૃષ્ણાસ્ત્ટકમ</t>
+  </si>
+  <si>
+    <t>શ્રીકૃષ્ણાસ્ત્ટકમ</t>
+  </si>
+  <si>
+    <t>ગીતા ના પંચપ્રાણ માનો પ્રથમ પ્રાણ એટલે પ્રયત્નાવાદ.</t>
+  </si>
+  <si>
+    <t>સાચું</t>
+  </si>
+  <si>
+    <t>ખોટું</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> A અને C બન્ને</t>
+  </si>
+  <si>
+    <t>"નિંદા - સ્તુતિ બંને ખોટા"  અને  "તો પછી ઘમંડ શાને?" આ બંને વાત ગીતાજી ના ક્યાં પ્રાણ માં થી શીખવા મળે છે?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">પ્રયત્નવાદ </t>
+  </si>
+  <si>
+    <t>અહંકારનાશ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ભક્તિ </t>
+  </si>
+  <si>
+    <t>સમન્વય</t>
+  </si>
+  <si>
+    <t>ગીતાજી નો એક પ્રાણ એટલે લોકસંગ્રહ, જેનો અર્થ એટલે.....</t>
+  </si>
+  <si>
+    <t>લોકો નુ ભેગું થવું</t>
+  </si>
+  <si>
+    <t>લોકોને મળવા જવું</t>
+  </si>
+  <si>
+    <t xml:space="preserve">લોકો સાથે સંબંધ બાંધવો </t>
+  </si>
+  <si>
+    <t>લોકો નુ ઉન્નતીકરણ</t>
+  </si>
+  <si>
+    <t>કર્મયોગી ના હાથ, જ્ઞાનીનીઆંખો અનેભક્ત નું હૃદય આ ત્રણે વાતો નો સમન્વય એટલે</t>
+  </si>
+  <si>
+    <t>આદર્શ નેતા</t>
+  </si>
+  <si>
+    <t>આદર્શભાઈ</t>
+  </si>
+  <si>
+    <t>આદર્શ પુરુષ</t>
+  </si>
+  <si>
+    <t>આદર્શ મિત્ર</t>
+  </si>
+  <si>
+    <t>ગીતા ના પંચપ્રાણ</t>
+  </si>
+  <si>
+    <t>ભરત</t>
+  </si>
+  <si>
+    <t>दादाजी એ કોને ભક્તિ ના 'બાદશાહ' કહ્યા છે?</t>
+  </si>
+  <si>
+    <t>ગૌદ્પદાચાર્ય</t>
+  </si>
+  <si>
+    <t>"सृष्टिर्मधुरा" આ સૃષ્ટિ મધુર છે - આવું કોને લાગે છે.</t>
+  </si>
+  <si>
+    <t>કવિ</t>
+  </si>
+  <si>
+    <t>કર્મયોગી</t>
+  </si>
+  <si>
+    <t>ભક્ત</t>
+  </si>
+  <si>
+    <t>સમાજસેવક</t>
+  </si>
+  <si>
+    <t>"वलितं" શબ્દ નો અર્થ શું થાય છે?</t>
+  </si>
+  <si>
+    <t>ભરેલું અથવા વ્યાપ્ત</t>
+  </si>
+  <si>
+    <t>ફરતા રહેવું</t>
+  </si>
+  <si>
+    <t>વાતો કરવી</t>
+  </si>
+  <si>
+    <t>પ્રેમ કરવો</t>
+  </si>
+  <si>
+    <t>મધુરાષ્ટકમ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="[$-7000447]0"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -385,13 +1163,38 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -403,13 +1206,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -418,8 +1221,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -698,50 +1530,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:I76"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="101.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20.140625" customWidth="1"/>
     <col min="4" max="4" width="26.28515625" customWidth="1"/>
     <col min="5" max="5" width="35.140625" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" style="1" customWidth="1"/>
     <col min="7" max="7" width="35.5703125" customWidth="1"/>
     <col min="8" max="8" width="37" customWidth="1"/>
     <col min="9" max="9" width="16.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>106</v>
+      <c r="G1" s="17" t="s">
+        <v>101</v>
       </c>
       <c r="H1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>100</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -754,544 +1586,1978 @@
       <c r="D2" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
-        <v>8</v>
+      <c r="E2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>104</v>
+        <v>17</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="I2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
         <v>12</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>14</v>
-      </c>
       <c r="F3" s="1" t="s">
-        <v>11</v>
+        <v>212</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>105</v>
+        <v>18</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>152</v>
       </c>
       <c r="I3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>15</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
       <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
         <v>20</v>
       </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" t="s">
-        <v>21</v>
+      <c r="F4" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>104</v>
+        <v>26</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="I4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
+      <c r="D5" t="s">
+        <v>319</v>
+      </c>
+      <c r="E5" t="s">
+        <v>320</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="I5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" t="s">
         <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
       </c>
       <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G6" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>107</v>
+      <c r="H6" s="5" t="s">
+        <v>175</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" t="s">
         <v>30</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>31</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>32</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>33</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G7" t="s">
         <v>34</v>
       </c>
-      <c r="F7" t="s">
-        <v>34</v>
-      </c>
-      <c r="G7" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>104</v>
+      <c r="H7" s="3" t="s">
+        <v>175</v>
       </c>
       <c r="I7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="C8" t="s">
         <v>37</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
+        <v>314</v>
+      </c>
+      <c r="E8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" t="s">
         <v>38</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" t="s">
-        <v>39</v>
-      </c>
       <c r="H8" t="s">
-        <v>105</v>
+        <v>175</v>
       </c>
       <c r="I8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="F9" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G9" t="s">
-        <v>54</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>104</v>
+        <v>53</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="I9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="s">
         <v>47</v>
       </c>
-      <c r="D10" t="s">
-        <v>48</v>
+      <c r="E10" t="s">
+        <v>317</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H10" t="s">
-        <v>105</v>
+        <v>170</v>
       </c>
       <c r="I10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>48</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" t="s">
         <v>50</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>51</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>52</v>
       </c>
-      <c r="E11" t="s">
-        <v>53</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H11" t="s">
-        <v>105</v>
+        <v>170</v>
       </c>
       <c r="I11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" t="s">
         <v>56</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" t="s">
-        <v>59</v>
-      </c>
-      <c r="D12" t="s">
-        <v>57</v>
-      </c>
       <c r="E12" t="s">
-        <v>58</v>
+        <v>316</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>60</v>
+        <v>315</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>104</v>
+        <v>34</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>175</v>
       </c>
       <c r="I12">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" t="s">
         <v>61</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="D13" t="s">
         <v>62</v>
       </c>
-      <c r="C13" t="s">
+      <c r="E13" t="s">
         <v>63</v>
       </c>
-      <c r="D13" t="s">
-        <v>64</v>
-      </c>
-      <c r="E13" t="s">
-        <v>65</v>
-      </c>
       <c r="F13" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="I13">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>64</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" t="s">
         <v>66</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="D14" t="s">
         <v>67</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="E14" t="s">
         <v>68</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="F14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" t="s">
         <v>69</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" t="s">
-        <v>71</v>
-      </c>
       <c r="H14" t="s">
-        <v>107</v>
+        <v>152</v>
       </c>
       <c r="I14">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C15" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="D15" t="s">
         <v>73</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>75</v>
+      <c r="E15" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H15" t="s">
-        <v>105</v>
+        <v>152</v>
       </c>
       <c r="I15">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B16" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>75</v>
+      <c r="E16" t="s">
+        <v>79</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>104</v>
+        <v>69</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>152</v>
       </c>
       <c r="I16">
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="D17" t="s">
         <v>78</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="E17" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="F17" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H17" t="s">
-        <v>107</v>
+        <v>175</v>
       </c>
       <c r="I17">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
+      </c>
+      <c r="C18" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" t="s">
+        <v>84</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>104</v>
+        <v>69</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>170</v>
       </c>
       <c r="I18">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E19" t="s">
         <v>88</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H19" t="s">
-        <v>105</v>
+        <v>170</v>
       </c>
       <c r="I19">
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>313</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C20" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" t="s">
         <v>91</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="E20" t="s">
         <v>92</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="F20" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G20" t="s">
         <v>93</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" t="s">
-        <v>96</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>104</v>
+      <c r="H20" s="3" t="s">
+        <v>152</v>
       </c>
       <c r="I20">
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>94</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
         <v>97</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="E21" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="F21" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21" t="s">
         <v>99</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G21" t="s">
-        <v>102</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>104</v>
+      <c r="H21" s="3" t="s">
+        <v>175</v>
       </c>
       <c r="I21">
         <v>20</v>
       </c>
     </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" t="s">
+        <v>105</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G22" t="s">
+        <v>107</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>109</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" t="s">
+        <v>111</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" t="s">
+        <v>113</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" t="s">
+        <v>107</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" t="s">
+        <v>118</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" t="s">
+        <v>26</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>119</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C25" t="s">
+        <v>121</v>
+      </c>
+      <c r="D25" t="s">
+        <v>122</v>
+      </c>
+      <c r="E25" t="s">
+        <v>123</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="G25" t="s">
+        <v>26</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>124</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C26" t="s">
+        <v>127</v>
+      </c>
+      <c r="D26" t="s">
+        <v>126</v>
+      </c>
+      <c r="E26" t="s">
+        <v>128</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G26" t="s">
+        <v>26</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>129</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D27" t="s">
+        <v>132</v>
+      </c>
+      <c r="E27" t="s">
+        <v>133</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G27" t="s">
+        <v>26</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>134</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E28" t="s">
+        <v>137</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="G28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>312</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="G29" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>143</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C30" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G30" t="s">
+        <v>26</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>145</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C31" t="s">
+        <v>147</v>
+      </c>
+      <c r="D31" t="s">
+        <v>148</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="G31" t="s">
+        <v>26</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>150</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C32" t="s">
+        <v>147</v>
+      </c>
+      <c r="D32" t="s">
+        <v>148</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="G32" t="s">
+        <v>26</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>153</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C33" t="s">
+        <v>110</v>
+      </c>
+      <c r="D33" t="s">
+        <v>154</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="G33" t="s">
+        <v>26</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="C34" t="s">
+        <v>341</v>
+      </c>
+      <c r="D34" t="s">
+        <v>157</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="G34" t="s">
+        <v>26</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>160</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="D35" t="s">
+        <v>162</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="G35" t="s">
+        <v>26</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>311</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C36" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G36" t="s">
+        <v>26</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>168</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D37" t="s">
+        <v>98</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="G37" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>310</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="C38" t="s">
+        <v>172</v>
+      </c>
+      <c r="D38" t="s">
+        <v>173</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>309</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="D39" t="s">
+        <v>173</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>176</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>181</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>186</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>191</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>196</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>199</v>
+      </c>
+      <c r="B45" t="s">
+        <v>200</v>
+      </c>
+      <c r="C45" t="s">
+        <v>201</v>
+      </c>
+      <c r="D45" t="s">
+        <v>202</v>
+      </c>
+      <c r="E45" t="s">
+        <v>203</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G45" t="s">
+        <v>204</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>308</v>
+      </c>
+      <c r="B46" t="s">
+        <v>205</v>
+      </c>
+      <c r="C46" t="s">
+        <v>206</v>
+      </c>
+      <c r="D46" t="s">
+        <v>207</v>
+      </c>
+      <c r="E46" t="s">
+        <v>208</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="G46" t="s">
+        <v>204</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>209</v>
+      </c>
+      <c r="B47" t="s">
+        <v>210</v>
+      </c>
+      <c r="C47" t="s">
+        <v>211</v>
+      </c>
+      <c r="D47" t="s">
+        <v>212</v>
+      </c>
+      <c r="E47" t="s">
+        <v>11</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="G47" t="s">
+        <v>213</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>214</v>
+      </c>
+      <c r="B48" t="s">
+        <v>215</v>
+      </c>
+      <c r="C48" t="s">
+        <v>216</v>
+      </c>
+      <c r="D48" t="s">
+        <v>217</v>
+      </c>
+      <c r="E48" t="s">
+        <v>218</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G48" t="s">
+        <v>219</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>220</v>
+      </c>
+      <c r="B49" t="s">
+        <v>221</v>
+      </c>
+      <c r="C49" t="s">
+        <v>222</v>
+      </c>
+      <c r="D49" t="s">
+        <v>223</v>
+      </c>
+      <c r="E49" t="s">
+        <v>224</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="G49" t="s">
+        <v>225</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>226</v>
+      </c>
+      <c r="B50" t="s">
+        <v>227</v>
+      </c>
+      <c r="C50" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50" t="s">
+        <v>96</v>
+      </c>
+      <c r="E50" t="s">
+        <v>228</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G50" t="s">
+        <v>204</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>229</v>
+      </c>
+      <c r="B51" s="13">
+        <v>50</v>
+      </c>
+      <c r="C51" s="13">
+        <v>60</v>
+      </c>
+      <c r="D51" s="13">
+        <v>64</v>
+      </c>
+      <c r="E51" s="13">
+        <v>48</v>
+      </c>
+      <c r="F51" s="14">
+        <v>48</v>
+      </c>
+      <c r="G51" t="s">
+        <v>219</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>307</v>
+      </c>
+      <c r="B52" t="s">
+        <v>230</v>
+      </c>
+      <c r="C52" t="s">
+        <v>231</v>
+      </c>
+      <c r="D52" t="s">
+        <v>232</v>
+      </c>
+      <c r="E52" t="s">
+        <v>233</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="G52" t="s">
+        <v>219</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>234</v>
+      </c>
+      <c r="B53" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" t="s">
+        <v>7</v>
+      </c>
+      <c r="E53" t="s">
+        <v>235</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G53" t="s">
+        <v>236</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>237</v>
+      </c>
+      <c r="B54" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" t="s">
+        <v>27</v>
+      </c>
+      <c r="D54" t="s">
+        <v>238</v>
+      </c>
+      <c r="E54" t="s">
+        <v>239</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="G54" t="s">
+        <v>236</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>240</v>
+      </c>
+      <c r="B55" t="s">
+        <v>241</v>
+      </c>
+      <c r="C55" t="s">
+        <v>242</v>
+      </c>
+      <c r="D55" t="s">
+        <v>243</v>
+      </c>
+      <c r="E55" t="s">
+        <v>244</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="G55" t="s">
+        <v>219</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>245</v>
+      </c>
+      <c r="B56" t="s">
+        <v>246</v>
+      </c>
+      <c r="C56" t="s">
+        <v>25</v>
+      </c>
+      <c r="D56" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" t="s">
+        <v>235</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="G56" t="s">
+        <v>236</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>247</v>
+      </c>
+      <c r="B57" t="s">
+        <v>248</v>
+      </c>
+      <c r="C57" t="s">
+        <v>249</v>
+      </c>
+      <c r="D57" t="s">
+        <v>250</v>
+      </c>
+      <c r="E57" t="s">
+        <v>251</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="G57" t="s">
+        <v>204</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>252</v>
+      </c>
+      <c r="B58" t="s">
+        <v>253</v>
+      </c>
+      <c r="C58" t="s">
+        <v>254</v>
+      </c>
+      <c r="D58" t="s">
+        <v>255</v>
+      </c>
+      <c r="E58" t="s">
+        <v>256</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G58" t="s">
+        <v>236</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>257</v>
+      </c>
+      <c r="B59" t="s">
+        <v>258</v>
+      </c>
+      <c r="C59" t="s">
+        <v>259</v>
+      </c>
+      <c r="D59" t="s">
+        <v>260</v>
+      </c>
+      <c r="E59" t="s">
+        <v>261</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G59" t="s">
+        <v>99</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>262</v>
+      </c>
+      <c r="B60" t="s">
+        <v>96</v>
+      </c>
+      <c r="C60" t="s">
+        <v>95</v>
+      </c>
+      <c r="D60" t="s">
+        <v>263</v>
+      </c>
+      <c r="E60" t="s">
+        <v>264</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="G60" t="s">
+        <v>99</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>265</v>
+      </c>
+      <c r="B61" t="s">
+        <v>266</v>
+      </c>
+      <c r="C61" t="s">
+        <v>267</v>
+      </c>
+      <c r="D61" t="s">
+        <v>268</v>
+      </c>
+      <c r="E61" t="s">
+        <v>261</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="G61" t="s">
+        <v>204</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>269</v>
+      </c>
+      <c r="B62" t="s">
+        <v>270</v>
+      </c>
+      <c r="C62" t="s">
+        <v>271</v>
+      </c>
+      <c r="D62" t="s">
+        <v>272</v>
+      </c>
+      <c r="E62" t="s">
+        <v>273</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="G62" t="s">
+        <v>99</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>274</v>
+      </c>
+      <c r="B63" t="s">
+        <v>275</v>
+      </c>
+      <c r="C63" t="s">
+        <v>276</v>
+      </c>
+      <c r="D63" t="s">
+        <v>277</v>
+      </c>
+      <c r="E63" t="s">
+        <v>278</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="G63" t="s">
+        <v>99</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>279</v>
+      </c>
+      <c r="B64" t="s">
+        <v>30</v>
+      </c>
+      <c r="C64" t="s">
+        <v>280</v>
+      </c>
+      <c r="D64" t="s">
+        <v>77</v>
+      </c>
+      <c r="E64" t="s">
+        <v>221</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G64" t="s">
+        <v>236</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>306</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="C65" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="E65" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="G65" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>286</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="C66" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="E66" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="G66" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>291</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="C67" s="9" t="s">
+        <v>293</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="E67" s="9" t="s">
+        <v>295</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>295</v>
+      </c>
+      <c r="G67" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C68" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="E68" s="9" t="s">
+        <v>300</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>297</v>
+      </c>
+      <c r="G68" s="9" t="s">
+        <v>285</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="D69" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E69" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>302</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="B70" s="12" t="s">
+        <v>322</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>323</v>
+      </c>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10"/>
+      <c r="F70" s="11" t="s">
+        <v>322</v>
+      </c>
+      <c r="G70" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="D71" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="E71" s="10" t="s">
+        <v>329</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>327</v>
+      </c>
+      <c r="G71" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>330</v>
+      </c>
+      <c r="B72" t="s">
+        <v>331</v>
+      </c>
+      <c r="C72" t="s">
+        <v>332</v>
+      </c>
+      <c r="D72" t="s">
+        <v>333</v>
+      </c>
+      <c r="E72" t="s">
+        <v>334</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="G72" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>335</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>338</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>339</v>
+      </c>
+      <c r="F73" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>340</v>
+      </c>
+      <c r="H73" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>342</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="D74" s="12" t="s">
+        <v>343</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="F74" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="G74" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="H74" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>344</v>
+      </c>
+      <c r="B75" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>346</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>347</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>348</v>
+      </c>
+      <c r="F75" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="G75" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>349</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>350</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="D76" s="12" t="s">
+        <v>352</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>353</v>
+      </c>
+      <c r="F76" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="G76" s="9" t="s">
+        <v>354</v>
+      </c>
+      <c r="H76" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:I76"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/storage/seeders/questions.xlsx
+++ b/storage/seeders/questions.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="895" uniqueCount="529">
   <si>
     <t>પ્રશ્ન</t>
   </si>
@@ -1126,6 +1126,528 @@
   <si>
     <t>મધુરાષ્ટકમ</t>
   </si>
+  <si>
+    <t>રામેશ્વર ના દર્શન કરતા પહેલા કોને પગે લાગવામાં આવે છે?</t>
+  </si>
+  <si>
+    <t>મલ્લિકાર્જુન</t>
+  </si>
+  <si>
+    <t>હનુમતીશ્વર</t>
+  </si>
+  <si>
+    <t>મહાકાલ</t>
+  </si>
+  <si>
+    <t>ત્રયંબકેશ્વર મહાદેવ ની ત્રીજી આંખ ભક્ત ને માટે શેનું સુચન કરે છે?</t>
+  </si>
+  <si>
+    <t>કર્તવ્યદક્ષતા</t>
+  </si>
+  <si>
+    <t>વાત્સલ્ય</t>
+  </si>
+  <si>
+    <t>બાલીશતા</t>
+  </si>
+  <si>
+    <t>આજે કોઈ ને પોતાનું ગોત્ર ખબર ન હોય તો તેને ક્યાં ગોત્ર નું ઉચ્ચારણ કરવાની શાસ્ત્ર અનુંમતી આપે છે?</t>
+  </si>
+  <si>
+    <t>ગૌતમ</t>
+  </si>
+  <si>
+    <t>વૈદ્યનાથ જ્યોતિર્લીંગ ની સ્થાપના કોને કરી છે?</t>
+  </si>
+  <si>
+    <t>પાર્વતી</t>
+  </si>
+  <si>
+    <t>ગણપતિ</t>
+  </si>
+  <si>
+    <t>રામ</t>
+  </si>
+  <si>
+    <t>વિશ્વ ને સૌપ્રથમ લોકશાહી નો સિધ્ધાંત કોને આપ્યો?</t>
+  </si>
+  <si>
+    <t>જમદગ્નિ</t>
+  </si>
+  <si>
+    <t>કેદારનાથ જ્યોતિર્લીંગ માં નર-નારાયણે શેનું ઉદગાન કર્યું છે?</t>
+  </si>
+  <si>
+    <t>શ્રીસૂક્ત</t>
+  </si>
+  <si>
+    <t>પુરુષસૂક્ત</t>
+  </si>
+  <si>
+    <t>પર્જન્યસૂક્ત</t>
+  </si>
+  <si>
+    <t>મંત્રસુક્ત</t>
+  </si>
+  <si>
+    <t>ગાયમાં ૩૩ કરોડ દેવતા છે એ ભાવનાત્મક વિચાર ક્યાં ઋષી એ આપ્યો?</t>
+  </si>
+  <si>
+    <t>ભરદ્વાજ</t>
+  </si>
+  <si>
+    <t>યાજ્ઞવલ્ક્ય એ સૂર્ય પાસેથી વિચાર અને સરસ્વતી પાસેથી શબ્દ મેળવીને ક્યાં ગ્રંથની રચના કરી?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">અથર્વવેદ </t>
+  </si>
+  <si>
+    <t>સામવેદ</t>
+  </si>
+  <si>
+    <t>શુક્લ યજુર્વેદ</t>
+  </si>
+  <si>
+    <t>કૃષ્ણ યજુર્વેદ</t>
+  </si>
+  <si>
+    <t>ક્યાં જ્યોતિર્લીંગ માં અર્ધનારીનટેશ્વર બનીને ભગવાને દર્શન આપ્યા?</t>
+  </si>
+  <si>
+    <t>નાગેશ્વર</t>
+  </si>
+  <si>
+    <t>મહાકાલેશ્વર</t>
+  </si>
+  <si>
+    <t>વૈદ્યનાથ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">દાદાજીને ટેમ્પલટન એવોર્ડ કઈ સાલમાં મળ્યો હતો? </t>
+  </si>
+  <si>
+    <t>વલભાચાર્યએ આપેલી બાળભક્તિ પાછળના મુખ્ય હેતુ કયા હતા?</t>
+  </si>
+  <si>
+    <t>બાળક પાસે મંગાઈ નહીં</t>
+  </si>
+  <si>
+    <t>બાળક પાસે રડાઈ નહીં</t>
+  </si>
+  <si>
+    <t>બાળક ની મૂર્તિ મનોહર લાગે</t>
+  </si>
+  <si>
+    <t>A અને B બન્ને</t>
+  </si>
+  <si>
+    <t>પૂજનીય દાદાજીએ અર્થશાસ્ત્ર પર આપેલું પુસ્તક કયું?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">શ્રીસુક્તમ </t>
+  </si>
+  <si>
+    <t>સંસ્કૃતિ ચિંતન</t>
+  </si>
+  <si>
+    <t>ભારતીયો નું આદર્શ જીવન</t>
+  </si>
+  <si>
+    <t>તુલસીદલ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">who is father of Indian philosophy? </t>
+  </si>
+  <si>
+    <t>વસિષ્ઠ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">પૂજનીય દાદાજીની પ્રિય રમત </t>
+  </si>
+  <si>
+    <t>હુતુતુ</t>
+  </si>
+  <si>
+    <t>કુસ્તી</t>
+  </si>
+  <si>
+    <t>આટીયા-પાટિયા</t>
+  </si>
+  <si>
+    <t>વોલીબોલ</t>
+  </si>
+  <si>
+    <t>વિદ્યાપ્રેમવર્ધન પરીક્ષામાં પાંચમી પરીક્ષા કઈ છે?</t>
+  </si>
+  <si>
+    <t>પારંગત</t>
+  </si>
+  <si>
+    <t>અનુજ્ઞાતા</t>
+  </si>
+  <si>
+    <t>વિચક્ષણ</t>
+  </si>
+  <si>
+    <t>જ્ઞાતા</t>
+  </si>
+  <si>
+    <t>ભગવાન શ્રીકૃષ્ણના ધનુષ્યનું નામ શું હતું?</t>
+  </si>
+  <si>
+    <t>પાંચજન્ય</t>
+  </si>
+  <si>
+    <t xml:space="preserve">સારંગ </t>
+  </si>
+  <si>
+    <t>પીનાકી</t>
+  </si>
+  <si>
+    <t>કોદંડ</t>
+  </si>
+  <si>
+    <t>માખણ ચોર ની વિચારધારાને પ્રગટ કરતો દાદાજીએ કયો પ્રયોગ આપ્યો?</t>
+  </si>
+  <si>
+    <t>ગોરસ</t>
+  </si>
+  <si>
+    <t>ગૌરીપૂજા</t>
+  </si>
+  <si>
+    <t>એક્વીરા</t>
+  </si>
+  <si>
+    <t>વિદ્યાપીઠ ના બે વર્ષના કોર્સ નું નામ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">આર્યવૃત </t>
+  </si>
+  <si>
+    <t>વિનીત</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ગુરુ દત્તાત્રેય એ કેટલા ગુરુઓ માન્યા હતા? </t>
+  </si>
+  <si>
+    <t xml:space="preserve">પૂજનીય દીદીજીને શિક્ષણ અંગે કયો એવોર્ડ મળ્યો? </t>
+  </si>
+  <si>
+    <t>લોકશિક્ષક એવોર્ડ</t>
+  </si>
+  <si>
+    <t>લોકજાગૃતિ એવોર્ડ</t>
+  </si>
+  <si>
+    <t>લોકસુધારક એવોર્ડ</t>
+  </si>
+  <si>
+    <t>લોકસેવા એવોર્ડ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">પૂજનીય દાદાજીના પ્રવચનોમાંથી મહાભારત પર લખાયેલું પુસ્તક કયું? </t>
+  </si>
+  <si>
+    <t>વ્યાસ વિચાર</t>
+  </si>
+  <si>
+    <t>જીવનતીર્થ</t>
+  </si>
+  <si>
+    <t>પૂજનીય દીદીજી એ પ્રથમ ઉદબોધન ક્યારે કર્યું?</t>
+  </si>
+  <si>
+    <t>ભાવમિલન સમારોહ ૧૯૭૬</t>
+  </si>
+  <si>
+    <t>તીર્થરાજ મિલન ૧૯૮૬</t>
+  </si>
+  <si>
+    <t>સુધાવર્ષ ૨૦૦૧</t>
+  </si>
+  <si>
+    <t>અશીતિ વંદના ૨૦૦૦</t>
+  </si>
+  <si>
+    <t>પ્રથમ મત્સ્યગંધાનુ જલાવરણ કયા વર્ષમાં થયું હતું?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">દાદાજીની પાંચ પેઢીના નામ ક્રમશઃ જણાવો </t>
+  </si>
+  <si>
+    <t>પાંડુરંગપંત – પરશુરામપંત – લક્ષ્મણરાવ – વૈજનાથ –પાંડુરંગશાસ્ત્રી</t>
+  </si>
+  <si>
+    <t>લક્ષ્મણરાવ – પરશુરામપંત – પાંડુરંગપંત – વૈજનાથ –પાંડુરંગશાસ્ત્રી</t>
+  </si>
+  <si>
+    <t>લક્ષ્મણરાવ – પાંડુરંગપંત – પરશુરામપંત – વૈજનાથ –પાંડુરંગશાસ્ત્રી</t>
+  </si>
+  <si>
+    <t xml:space="preserve">દાદાજીએ આગરી લોકોને આપેલો પ્રયોગ </t>
+  </si>
+  <si>
+    <t>એકવીરા</t>
+  </si>
+  <si>
+    <t>ઘરમંદિર</t>
+  </si>
+  <si>
+    <t xml:space="preserve">મારા દીદી બતાવે જે રીતે.... ' આ ભાવગીત કઈ કેસેટમાં છે? </t>
+  </si>
+  <si>
+    <t>ન ત્વયા વિના</t>
+  </si>
+  <si>
+    <t>અશીતિ</t>
+  </si>
+  <si>
+    <t>તેજમિદમ્</t>
+  </si>
+  <si>
+    <t>નમઃ તે</t>
+  </si>
+  <si>
+    <t>ગણપતિના ઉત્સવને સામાજિક રૂપ આપનાર કોણ? </t>
+  </si>
+  <si>
+    <t>લોકમાન્ય તિલક</t>
+  </si>
+  <si>
+    <t>લાલા લજપતરાય</t>
+  </si>
+  <si>
+    <t>વીર સાવરકર</t>
+  </si>
+  <si>
+    <t>દયાનંદ સરસ્વતી</t>
+  </si>
+  <si>
+    <t>શ્રીરામરક્ષાસ્તોત્ર ના રચયિતા કોણ છે?</t>
+  </si>
+  <si>
+    <t>બુદ્ધકૌશિકમુનિ</t>
+  </si>
+  <si>
+    <t>ખંડનખંડખાદ્ય ગ્રંથના રચયિતા કોણ?</t>
+  </si>
+  <si>
+    <t>કાલિદાસ</t>
+  </si>
+  <si>
+    <t>ભવભૂતિ</t>
+  </si>
+  <si>
+    <t>ગુણાઢ્ય</t>
+  </si>
+  <si>
+    <t xml:space="preserve">સાત લાખ શ્લોક ધરાવતો પૈશાચી ભાષામાં લખાયેલ ગ્રંથ ના રચયિતા કોણ? </t>
+  </si>
+  <si>
+    <t>જીવનમાં કૃતજ્ઞતા નિર્માણ થાય એ માટે દાદાજીએ કઈ વાત આપી? </t>
+  </si>
+  <si>
+    <t>ભાવફેરી</t>
+  </si>
+  <si>
+    <t>ભક્તિફેરી</t>
+  </si>
+  <si>
+    <t>ત્રિકાળ સંધ્યા</t>
+  </si>
+  <si>
+    <t xml:space="preserve">વાચસ્પતિ મિશ્ર એ રચેલ ગ્રંથનું નામ </t>
+  </si>
+  <si>
+    <t>ખંડનખંડખાદ્ય</t>
+  </si>
+  <si>
+    <t>નૈષધ</t>
+  </si>
+  <si>
+    <t>ભામતી</t>
+  </si>
+  <si>
+    <t xml:space="preserve">યુવાકેન્દ્રની શરૂઆત કઈ સાલમાં થઇ? </t>
+  </si>
+  <si>
+    <t>વિદ્યાપ્રેમવર્ધન પરીક્ષાની શરૂઆત ક્યારથી થઈ?</t>
+  </si>
+  <si>
+    <t>સ્વાધ્યાય પરિવાર ના જિલ્લાના મુખ્ય કાર્યાલયને શું કહીએ છીએ?</t>
+  </si>
+  <si>
+    <t>નિર્મળ નિકેતન</t>
+  </si>
+  <si>
+    <t>વિમલ જ્યોતિ</t>
+  </si>
+  <si>
+    <t>પાર્થપ્રીતિ</t>
+  </si>
+  <si>
+    <t>આમાંથી એક પણ નહિ</t>
+  </si>
+  <si>
+    <t>ભાગવત પુરાણ માં કેટલા શ્લોકો છે?</t>
+  </si>
+  <si>
+    <t>નચિકેતા નું વર્ણન ક્યાં ઉપનિષદમાં આવે છે?</t>
+  </si>
+  <si>
+    <t>કેનોપનિષદ</t>
+  </si>
+  <si>
+    <t>ઈશાવાશ્યોપનીષદ</t>
+  </si>
+  <si>
+    <t>પ્રશ્નોપનિષદ</t>
+  </si>
+  <si>
+    <t>કઠોપનિષદ્</t>
+  </si>
+  <si>
+    <t>સાંદિપની ઋષિનો આશ્રમ કઈ નદીના કિનારે હતો?</t>
+  </si>
+  <si>
+    <t>કાવેરી</t>
+  </si>
+  <si>
+    <t>ક્ષિપ્રા</t>
+  </si>
+  <si>
+    <t>ગંગા</t>
+  </si>
+  <si>
+    <t>ભીષ્મપિતામહનુ મૂળ નામ</t>
+  </si>
+  <si>
+    <t>દેવવ્રત</t>
+  </si>
+  <si>
+    <t>રાધેય</t>
+  </si>
+  <si>
+    <t>દેવરત</t>
+  </si>
+  <si>
+    <t>દેવદત્ત</t>
+  </si>
+  <si>
+    <t>અભિમન્યુ ની પત્નીનું નામ</t>
+  </si>
+  <si>
+    <t>ઉત્તરા</t>
+  </si>
+  <si>
+    <t>ઊર્મિ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">કૃષ્ણના સારથી નું નામ </t>
+  </si>
+  <si>
+    <t>શલ્ય</t>
+  </si>
+  <si>
+    <t>ધૃષ્ટધ્રુમ્ન</t>
+  </si>
+  <si>
+    <t>વિરાટ</t>
+  </si>
+  <si>
+    <t>દારૂક</t>
+  </si>
+  <si>
+    <t xml:space="preserve">પ્લેટોના ગુરુ </t>
+  </si>
+  <si>
+    <t>કાર્લ માર્ક્સ</t>
+  </si>
+  <si>
+    <t>સોક્રેટિસ</t>
+  </si>
+  <si>
+    <t>જોહન આર્ક</t>
+  </si>
+  <si>
+    <t>ઈમર્સન</t>
+  </si>
+  <si>
+    <t xml:space="preserve">નવધા ભક્તિમાં બીજી ભક્તિ કઈ આવે છે? </t>
+  </si>
+  <si>
+    <t>कीर्तनम्</t>
+  </si>
+  <si>
+    <t xml:space="preserve">श्रवणम् </t>
+  </si>
+  <si>
+    <t xml:space="preserve">पादसेवनम् </t>
+  </si>
+  <si>
+    <t>सख्यम्</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ત્રિકાળ સંધ્યામાં ગીતાજીના શ્લોક કેટલા છે? </t>
+  </si>
+  <si>
+    <t>સ્વાધ્યાય પરિવારના કાર્યક્રમોમાં રાખવામાં આવતી પ્રાસંગિક ઓફિસ એટલે</t>
+  </si>
+  <si>
+    <t xml:space="preserve">યાતા યાત કાર્યાલય </t>
+  </si>
+  <si>
+    <t xml:space="preserve">પતંજલિ ચિકિત્સાલય </t>
+  </si>
+  <si>
+    <t>સુદામપુરી</t>
+  </si>
+  <si>
+    <t xml:space="preserve">અર્જુન કાર્યાલય </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ભીમના પૌત્ર નું નામ </t>
+  </si>
+  <si>
+    <t>ઘટોત્ઘચ</t>
+  </si>
+  <si>
+    <t>બર્બરીક</t>
+  </si>
+  <si>
+    <t>પરીક્ષિત</t>
+  </si>
+  <si>
+    <t>વિધાપીઠની સ્થાપના કયા વર્ષમાં થઇ?</t>
+  </si>
+  <si>
+    <t>વિદેશમાં સ્વાધ્યાય કાર્ય ક્યાં નામથી ચાલે છે?</t>
+  </si>
+  <si>
+    <t>Devine Association of Yogeshwar</t>
+  </si>
+  <si>
+    <t>Swadhyay Organization</t>
+  </si>
+  <si>
+    <t>Devine Society of Yogeshwar</t>
+  </si>
+  <si>
+    <t>Swadhyay Devine Family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">જીવનતીર્થ </t>
+  </si>
+  <si>
+    <t>hard</t>
+  </si>
+  <si>
+    <t>easy</t>
+  </si>
+  <si>
+    <t>medium</t>
+  </si>
 </sst>
 </file>
 
@@ -1135,7 +1657,7 @@
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="164" formatCode="[$-7000447]0"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1176,6 +1698,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1210,7 +1745,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -1248,6 +1783,16 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1530,7 +2075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I76"/>
+  <dimension ref="A1:I124"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="101.5703125" bestFit="1" customWidth="1"/>
@@ -3555,6 +4100,1164 @@
         <v>175</v>
       </c>
     </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="B77" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="C77" s="18" t="s">
+        <v>357</v>
+      </c>
+      <c r="D77" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="E77" s="18"/>
+      <c r="F77" s="18" t="s">
+        <v>357</v>
+      </c>
+      <c r="G77" s="18" t="s">
+        <v>525</v>
+      </c>
+      <c r="H77" s="18" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="18" t="s">
+        <v>359</v>
+      </c>
+      <c r="B78" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="C78" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="D78" s="18" t="s">
+        <v>362</v>
+      </c>
+      <c r="E78" s="18"/>
+      <c r="F78" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="G78" s="18" t="s">
+        <v>525</v>
+      </c>
+      <c r="H78" s="18" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="B79" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="C79" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="D79" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="E79" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="F79" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="G79" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="H79" s="18" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="B80" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="D80" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="E80" s="18" t="s">
+        <v>368</v>
+      </c>
+      <c r="F80" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="G80" s="18" t="s">
+        <v>525</v>
+      </c>
+      <c r="H80" s="18" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A81" s="18" t="s">
+        <v>369</v>
+      </c>
+      <c r="B81" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C81" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D81" s="18" t="s">
+        <v>370</v>
+      </c>
+      <c r="E81" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="F81" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="G81" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="H81" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A82" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="B82" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="C82" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="D82" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="E82" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="F82" s="18" t="s">
+        <v>373</v>
+      </c>
+      <c r="G82" s="18" t="s">
+        <v>525</v>
+      </c>
+      <c r="H82" s="18" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A83" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="B83" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D83" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="F83" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="G83" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="H83" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A84" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="B84" s="18" t="s">
+        <v>379</v>
+      </c>
+      <c r="C84" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="D84" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="E84" s="18" t="s">
+        <v>382</v>
+      </c>
+      <c r="F84" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="G84" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="H84" s="18" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A85" s="18" t="s">
+        <v>383</v>
+      </c>
+      <c r="B85" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="C85" s="18" t="s">
+        <v>385</v>
+      </c>
+      <c r="D85" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="E85" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="F85" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="G85" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="H85" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A86" s="18" t="s">
+        <v>387</v>
+      </c>
+      <c r="B86" s="18">
+        <v>1995</v>
+      </c>
+      <c r="C86" s="18">
+        <v>1996</v>
+      </c>
+      <c r="D86" s="18">
+        <v>1997</v>
+      </c>
+      <c r="E86" s="18">
+        <v>1998</v>
+      </c>
+      <c r="F86" s="18">
+        <v>1997</v>
+      </c>
+      <c r="G86" s="18"/>
+      <c r="H86" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="18" t="s">
+        <v>388</v>
+      </c>
+      <c r="B87" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="C87" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="D87" s="18" t="s">
+        <v>391</v>
+      </c>
+      <c r="E87" s="18" t="s">
+        <v>392</v>
+      </c>
+      <c r="F87" s="18" t="s">
+        <v>392</v>
+      </c>
+      <c r="G87" s="18"/>
+      <c r="H87" s="18" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A88" s="18" t="s">
+        <v>393</v>
+      </c>
+      <c r="B88" s="18" t="s">
+        <v>394</v>
+      </c>
+      <c r="C88" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="D88" s="18" t="s">
+        <v>396</v>
+      </c>
+      <c r="E88" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="F88" s="18" t="s">
+        <v>394</v>
+      </c>
+      <c r="G88" s="18"/>
+      <c r="H88" s="18" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A89" s="18" t="s">
+        <v>398</v>
+      </c>
+      <c r="B89" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="C89" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="D89" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="E89" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="F89" s="18" t="s">
+        <v>184</v>
+      </c>
+      <c r="G89" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="H89" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="B90" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="C90" s="18" t="s">
+        <v>402</v>
+      </c>
+      <c r="D90" s="18" t="s">
+        <v>403</v>
+      </c>
+      <c r="E90" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="F90" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="G90" s="18"/>
+      <c r="H90" s="18" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="B91" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="C91" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="D91" s="18" t="s">
+        <v>408</v>
+      </c>
+      <c r="E91" s="18" t="s">
+        <v>409</v>
+      </c>
+      <c r="F91" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="G91" s="18"/>
+      <c r="H91" s="18" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="B92" s="18" t="s">
+        <v>411</v>
+      </c>
+      <c r="C92" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="D92" s="18" t="s">
+        <v>413</v>
+      </c>
+      <c r="E92" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="F92" s="18" t="s">
+        <v>412</v>
+      </c>
+      <c r="G92" s="18"/>
+      <c r="H92" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="B93" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="C93" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="D93" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="E93" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="F93" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="G93" s="18"/>
+      <c r="H93" s="18" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="C94" s="18" t="s">
+        <v>421</v>
+      </c>
+      <c r="D94" s="18"/>
+      <c r="E94" s="18"/>
+      <c r="F94" s="18"/>
+      <c r="G94" s="18"/>
+      <c r="H94" s="18" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="18" t="s">
+        <v>422</v>
+      </c>
+      <c r="B95" s="18">
+        <v>23</v>
+      </c>
+      <c r="C95" s="18">
+        <v>22</v>
+      </c>
+      <c r="D95" s="18">
+        <v>21</v>
+      </c>
+      <c r="E95" s="18">
+        <v>24</v>
+      </c>
+      <c r="F95" s="18">
+        <v>24</v>
+      </c>
+      <c r="G95" s="18"/>
+      <c r="H95" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>424</v>
+      </c>
+      <c r="C96" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="D96" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="E96" s="18" t="s">
+        <v>427</v>
+      </c>
+      <c r="F96" s="18" t="s">
+        <v>424</v>
+      </c>
+      <c r="G96" s="18"/>
+      <c r="H96" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="B97" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="C97" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="D97" s="18" t="s">
+        <v>397</v>
+      </c>
+      <c r="E97" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="F97" s="18" t="s">
+        <v>429</v>
+      </c>
+      <c r="G97" s="18"/>
+      <c r="H97" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="B98" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="C98" s="18" t="s">
+        <v>433</v>
+      </c>
+      <c r="D98" s="18" t="s">
+        <v>434</v>
+      </c>
+      <c r="E98" s="18" t="s">
+        <v>435</v>
+      </c>
+      <c r="F98" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="G98" s="18"/>
+      <c r="H98" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="B99" s="18">
+        <v>1987</v>
+      </c>
+      <c r="C99" s="18">
+        <v>1988</v>
+      </c>
+      <c r="D99" s="18">
+        <v>1989</v>
+      </c>
+      <c r="E99" s="18">
+        <v>1990</v>
+      </c>
+      <c r="F99" s="18">
+        <v>1988</v>
+      </c>
+      <c r="G99" s="18"/>
+      <c r="H99" s="18" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="18" t="s">
+        <v>437</v>
+      </c>
+      <c r="B100" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="C100" s="18" t="s">
+        <v>439</v>
+      </c>
+      <c r="D100" s="18" t="s">
+        <v>440</v>
+      </c>
+      <c r="E100" s="18"/>
+      <c r="F100" s="18" t="s">
+        <v>438</v>
+      </c>
+      <c r="G100" s="18"/>
+      <c r="H100" s="18" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="18" t="s">
+        <v>441</v>
+      </c>
+      <c r="B101" s="18" t="s">
+        <v>442</v>
+      </c>
+      <c r="C101" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="D101" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="E101" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="F101" s="18" t="s">
+        <v>442</v>
+      </c>
+      <c r="G101" s="18"/>
+      <c r="H101" s="18" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="20" t="s">
+        <v>444</v>
+      </c>
+      <c r="B102" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="C102" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="D102" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="E102" s="18" t="s">
+        <v>448</v>
+      </c>
+      <c r="F102" s="18" t="s">
+        <v>447</v>
+      </c>
+      <c r="G102" s="18"/>
+      <c r="H102" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="B103" s="18" t="s">
+        <v>450</v>
+      </c>
+      <c r="C103" s="18" t="s">
+        <v>451</v>
+      </c>
+      <c r="D103" s="18" t="s">
+        <v>452</v>
+      </c>
+      <c r="E103" s="18" t="s">
+        <v>453</v>
+      </c>
+      <c r="F103" s="18" t="s">
+        <v>450</v>
+      </c>
+      <c r="G103" s="18"/>
+      <c r="H103" s="18" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="18" t="s">
+        <v>454</v>
+      </c>
+      <c r="B104" s="18" t="s">
+        <v>455</v>
+      </c>
+      <c r="C104" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="D104" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="E104" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="F104" s="18" t="s">
+        <v>455</v>
+      </c>
+      <c r="G104" s="18"/>
+      <c r="H104" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="18" t="s">
+        <v>456</v>
+      </c>
+      <c r="B105" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="C105" s="18" t="s">
+        <v>458</v>
+      </c>
+      <c r="D105" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="E105" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="F105" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="G105" s="18"/>
+      <c r="H105" s="18" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="18" t="s">
+        <v>460</v>
+      </c>
+      <c r="B106" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="C106" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="D106" s="18" t="s">
+        <v>253</v>
+      </c>
+      <c r="E106" s="18" t="s">
+        <v>458</v>
+      </c>
+      <c r="F106" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="G106" s="18"/>
+      <c r="H106" s="18" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="B107" s="18" t="s">
+        <v>462</v>
+      </c>
+      <c r="C107" s="18" t="s">
+        <v>463</v>
+      </c>
+      <c r="D107" s="18" t="s">
+        <v>464</v>
+      </c>
+      <c r="E107" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F107" s="21" t="s">
+        <v>464</v>
+      </c>
+      <c r="G107" s="18"/>
+      <c r="H107" s="18" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="18" t="s">
+        <v>465</v>
+      </c>
+      <c r="B108" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="C108" s="18" t="s">
+        <v>467</v>
+      </c>
+      <c r="D108" s="18" t="s">
+        <v>468</v>
+      </c>
+      <c r="E108" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F108" s="18" t="s">
+        <v>468</v>
+      </c>
+      <c r="G108" s="18"/>
+      <c r="H108" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="18" t="s">
+        <v>469</v>
+      </c>
+      <c r="B109" s="18">
+        <v>1980</v>
+      </c>
+      <c r="C109" s="18">
+        <v>1979</v>
+      </c>
+      <c r="D109" s="18">
+        <v>1978</v>
+      </c>
+      <c r="E109" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="F109" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="G109" s="18"/>
+      <c r="H109" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="22" t="s">
+        <v>470</v>
+      </c>
+      <c r="B110" s="23">
+        <v>1965</v>
+      </c>
+      <c r="C110" s="23">
+        <v>1966</v>
+      </c>
+      <c r="D110" s="23">
+        <v>1967</v>
+      </c>
+      <c r="E110" s="23">
+        <v>1968</v>
+      </c>
+      <c r="F110" s="23">
+        <v>1967</v>
+      </c>
+      <c r="G110" s="18"/>
+      <c r="H110" s="18" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="22" t="s">
+        <v>471</v>
+      </c>
+      <c r="B111" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="C111" s="22" t="s">
+        <v>473</v>
+      </c>
+      <c r="D111" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="E111" s="22" t="s">
+        <v>475</v>
+      </c>
+      <c r="F111" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="G111" s="18"/>
+      <c r="H111" s="22" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="22" t="s">
+        <v>476</v>
+      </c>
+      <c r="B112" s="23">
+        <v>14500</v>
+      </c>
+      <c r="C112" s="23">
+        <v>14600</v>
+      </c>
+      <c r="D112" s="23">
+        <v>13500</v>
+      </c>
+      <c r="E112" s="23">
+        <v>13600</v>
+      </c>
+      <c r="F112" s="23">
+        <v>14500</v>
+      </c>
+      <c r="G112" s="18"/>
+      <c r="H112" s="18" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="22" t="s">
+        <v>477</v>
+      </c>
+      <c r="B113" s="22" t="s">
+        <v>478</v>
+      </c>
+      <c r="C113" s="22" t="s">
+        <v>479</v>
+      </c>
+      <c r="D113" s="22" t="s">
+        <v>480</v>
+      </c>
+      <c r="E113" s="22" t="s">
+        <v>481</v>
+      </c>
+      <c r="F113" s="22" t="s">
+        <v>481</v>
+      </c>
+      <c r="G113" s="18"/>
+      <c r="H113" s="22" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="B114" s="22" t="s">
+        <v>483</v>
+      </c>
+      <c r="C114" s="22" t="s">
+        <v>484</v>
+      </c>
+      <c r="D114" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" s="22" t="s">
+        <v>485</v>
+      </c>
+      <c r="F114" s="22" t="s">
+        <v>484</v>
+      </c>
+      <c r="G114" s="18"/>
+      <c r="H114" s="22" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="22" t="s">
+        <v>486</v>
+      </c>
+      <c r="B115" s="22" t="s">
+        <v>487</v>
+      </c>
+      <c r="C115" s="22" t="s">
+        <v>488</v>
+      </c>
+      <c r="D115" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="E115" s="22" t="s">
+        <v>490</v>
+      </c>
+      <c r="F115" s="22" t="s">
+        <v>487</v>
+      </c>
+      <c r="G115" s="18"/>
+      <c r="H115" s="22" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" s="22" t="s">
+        <v>491</v>
+      </c>
+      <c r="B116" s="22" t="s">
+        <v>492</v>
+      </c>
+      <c r="C116" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D116" s="22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E116" s="22" t="s">
+        <v>493</v>
+      </c>
+      <c r="F116" s="22" t="s">
+        <v>492</v>
+      </c>
+      <c r="G116" s="18"/>
+      <c r="H116" s="22" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="22" t="s">
+        <v>494</v>
+      </c>
+      <c r="B117" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="C117" s="22" t="s">
+        <v>496</v>
+      </c>
+      <c r="D117" s="22" t="s">
+        <v>497</v>
+      </c>
+      <c r="E117" s="22" t="s">
+        <v>498</v>
+      </c>
+      <c r="F117" s="22" t="s">
+        <v>498</v>
+      </c>
+      <c r="G117" s="18"/>
+      <c r="H117" s="22" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="22" t="s">
+        <v>499</v>
+      </c>
+      <c r="B118" s="22" t="s">
+        <v>500</v>
+      </c>
+      <c r="C118" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="D118" s="22" t="s">
+        <v>502</v>
+      </c>
+      <c r="E118" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="F118" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="G118" s="18"/>
+      <c r="H118" s="22" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="22" t="s">
+        <v>504</v>
+      </c>
+      <c r="B119" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="C119" s="22" t="s">
+        <v>506</v>
+      </c>
+      <c r="D119" s="22" t="s">
+        <v>507</v>
+      </c>
+      <c r="E119" s="22" t="s">
+        <v>508</v>
+      </c>
+      <c r="F119" s="22" t="s">
+        <v>505</v>
+      </c>
+      <c r="G119" s="18"/>
+      <c r="H119" s="22" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="22" t="s">
+        <v>509</v>
+      </c>
+      <c r="B120" s="23">
+        <v>2</v>
+      </c>
+      <c r="C120" s="23">
+        <v>3</v>
+      </c>
+      <c r="D120" s="23">
+        <v>4</v>
+      </c>
+      <c r="E120" s="23">
+        <v>5</v>
+      </c>
+      <c r="F120" s="23">
+        <v>3</v>
+      </c>
+      <c r="G120" s="18"/>
+      <c r="H120" s="22" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" s="22" t="s">
+        <v>510</v>
+      </c>
+      <c r="B121" s="22" t="s">
+        <v>511</v>
+      </c>
+      <c r="C121" s="22" t="s">
+        <v>512</v>
+      </c>
+      <c r="D121" s="22" t="s">
+        <v>513</v>
+      </c>
+      <c r="E121" s="22" t="s">
+        <v>514</v>
+      </c>
+      <c r="F121" s="22" t="s">
+        <v>514</v>
+      </c>
+      <c r="G121" s="18"/>
+      <c r="H121" s="22" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" s="22" t="s">
+        <v>515</v>
+      </c>
+      <c r="B122" s="22" t="s">
+        <v>516</v>
+      </c>
+      <c r="C122" s="22" t="s">
+        <v>517</v>
+      </c>
+      <c r="D122" s="22" t="s">
+        <v>518</v>
+      </c>
+      <c r="E122" s="22"/>
+      <c r="F122" s="22" t="s">
+        <v>517</v>
+      </c>
+      <c r="G122" s="18"/>
+      <c r="H122" s="22" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" s="22" t="s">
+        <v>519</v>
+      </c>
+      <c r="B123" s="23">
+        <v>1926</v>
+      </c>
+      <c r="C123" s="23">
+        <v>1927</v>
+      </c>
+      <c r="D123" s="23">
+        <v>1956</v>
+      </c>
+      <c r="E123" s="23">
+        <v>1954</v>
+      </c>
+      <c r="F123" s="23">
+        <v>1956</v>
+      </c>
+      <c r="G123" s="18"/>
+      <c r="H123" s="22" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" s="22" t="s">
+        <v>520</v>
+      </c>
+      <c r="B124" s="22" t="s">
+        <v>521</v>
+      </c>
+      <c r="C124" s="22" t="s">
+        <v>522</v>
+      </c>
+      <c r="D124" s="22" t="s">
+        <v>523</v>
+      </c>
+      <c r="E124" s="22" t="s">
+        <v>524</v>
+      </c>
+      <c r="F124" s="22" t="s">
+        <v>521</v>
+      </c>
+      <c r="G124" s="18"/>
+      <c r="H124" s="22" t="s">
+        <v>526</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:I76"/>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/storage/seeders/questions.xlsx
+++ b/storage/seeders/questions.xlsx
@@ -7,11 +7,6 @@
   </sheets>
   <definedNames/>
   <calcPr/>
-  <extLst>
-    <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="EptBr2MmVIGqxqH8T6sHBFklPvx36UV3pN3V4FQ6oOc="/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 

--- a/storage/seeders/questions.xlsx
+++ b/storage/seeders/questions.xlsx
@@ -693,10 +693,10 @@
     <t>મેઘદૂત</t>
   </si>
   <si>
-    <t>શાન્કુતલ</t>
-  </si>
-  <si>
-    <t>કુમારસંભવમ</t>
+    <t>કુમારસંભવમ્</t>
+  </si>
+  <si>
+    <t>શાકુંતલમ્</t>
   </si>
   <si>
     <t>શિશુપાલવધ</t>
@@ -1675,7 +1675,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="11"/>
+      <color indexed="12"/>
       <name val="Inherit"/>
     </font>
     <font>
@@ -1685,7 +1685,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color indexed="11"/>
+      <color indexed="12"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -1714,7 +1714,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="12"/>
+        <fgColor indexed="11"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -1725,7 +1725,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -1832,13 +1832,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1854,34 +1885,34 @@
     <xf numFmtId="49" fontId="4" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="4" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="5" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1890,22 +1921,22 @@
     <xf numFmtId="49" fontId="7" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="4" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1965,6 +1996,24 @@
     <xf numFmtId="49" fontId="9" fillId="4" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="4" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1984,8 +2033,8 @@
       <rgbColor rgb="ff000000"/>
       <rgbColor rgb="ffffd965"/>
       <rgbColor rgb="ffaaaaaa"/>
+      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ff1f1f1f"/>
-      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ff70ad47"/>
       <rgbColor rgb="ff202122"/>
     </indexedColors>
@@ -2186,12 +2235,12 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -2223,10 +2272,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -2465,12 +2514,12 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="12700" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst/>
         <a:sp3d/>
@@ -2774,10 +2823,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Calibri"/>
-            <a:ea typeface="Calibri"/>
-            <a:cs typeface="Calibri"/>
-            <a:sym typeface="Calibri"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -8554,48 +8603,48 @@
       <c r="Z122" s="30"/>
     </row>
     <row r="123" ht="18" customHeight="1">
-      <c r="A123" t="s" s="39">
+      <c r="A123" t="s" s="42">
         <v>526</v>
       </c>
-      <c r="B123" t="s" s="36">
+      <c r="B123" t="s" s="43">
         <v>527</v>
       </c>
-      <c r="C123" t="s" s="36">
+      <c r="C123" t="s" s="43">
         <v>528</v>
       </c>
-      <c r="D123" t="s" s="36">
+      <c r="D123" t="s" s="43">
         <v>529</v>
       </c>
-      <c r="E123" t="s" s="36">
+      <c r="E123" t="s" s="43">
         <v>530</v>
       </c>
-      <c r="F123" t="s" s="36">
+      <c r="F123" t="s" s="43">
         <v>529</v>
       </c>
-      <c r="G123" s="29"/>
-      <c r="H123" t="s" s="40">
+      <c r="G123" s="44"/>
+      <c r="H123" t="s" s="45">
         <v>371</v>
       </c>
-      <c r="I123" s="28">
+      <c r="I123" s="46">
         <v>20</v>
       </c>
-      <c r="J123" s="29"/>
-      <c r="K123" s="29"/>
-      <c r="L123" s="29"/>
-      <c r="M123" s="29"/>
-      <c r="N123" s="29"/>
-      <c r="O123" s="29"/>
-      <c r="P123" s="29"/>
-      <c r="Q123" s="29"/>
-      <c r="R123" s="29"/>
-      <c r="S123" s="29"/>
-      <c r="T123" s="29"/>
-      <c r="U123" s="29"/>
-      <c r="V123" s="29"/>
-      <c r="W123" s="29"/>
-      <c r="X123" s="29"/>
-      <c r="Y123" s="29"/>
-      <c r="Z123" s="30"/>
+      <c r="J123" s="44"/>
+      <c r="K123" s="44"/>
+      <c r="L123" s="44"/>
+      <c r="M123" s="44"/>
+      <c r="N123" s="44"/>
+      <c r="O123" s="44"/>
+      <c r="P123" s="44"/>
+      <c r="Q123" s="44"/>
+      <c r="R123" s="44"/>
+      <c r="S123" s="44"/>
+      <c r="T123" s="44"/>
+      <c r="U123" s="44"/>
+      <c r="V123" s="44"/>
+      <c r="W123" s="44"/>
+      <c r="X123" s="44"/>
+      <c r="Y123" s="44"/>
+      <c r="Z123" s="47"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
